--- a/appium-tests/Automation_Test_Report.xlsx
+++ b/appium-tests/Automation_Test_Report.xlsx
@@ -458,7 +458,7 @@
         <v>Execution Date</v>
       </c>
       <c r="B7" t="str">
-        <v>22/7/2026, 11:13:15 am</v>
+        <v>22/7/2026, 9:59:57 pm</v>
       </c>
     </row>
     <row r="8">
@@ -605,7 +605,7 @@
         <v>PASS</v>
       </c>
       <c r="L2" t="str">
-        <v>0.082s</v>
+        <v>0.069s</v>
       </c>
       <c r="M2" t="str">
         <v>N/A</v>
@@ -648,7 +648,7 @@
         <v>PASS</v>
       </c>
       <c r="L3" t="str">
-        <v>0.051s</v>
+        <v>0.160s</v>
       </c>
       <c r="M3" t="str">
         <v>N/A</v>
@@ -691,7 +691,7 @@
         <v>PASS</v>
       </c>
       <c r="L4" t="str">
-        <v>0.170s</v>
+        <v>0.124s</v>
       </c>
       <c r="M4" t="str">
         <v>N/A</v>
@@ -777,7 +777,7 @@
         <v>PASS</v>
       </c>
       <c r="L6" t="str">
-        <v>0.067s</v>
+        <v>0.094s</v>
       </c>
       <c r="M6" t="str">
         <v>N/A</v>
@@ -820,7 +820,7 @@
         <v>PASS</v>
       </c>
       <c r="L7" t="str">
-        <v>0.059s</v>
+        <v>0.060s</v>
       </c>
       <c r="M7" t="str">
         <v>N/A</v>
@@ -863,7 +863,7 @@
         <v>PASS</v>
       </c>
       <c r="L8" t="str">
-        <v>0.160s</v>
+        <v>0.188s</v>
       </c>
       <c r="M8" t="str">
         <v>N/A</v>
@@ -906,7 +906,7 @@
         <v>PASS</v>
       </c>
       <c r="L9" t="str">
-        <v>0.063s</v>
+        <v>0.186s</v>
       </c>
       <c r="M9" t="str">
         <v>N/A</v>
@@ -949,7 +949,7 @@
         <v>PASS</v>
       </c>
       <c r="L10" t="str">
-        <v>0.163s</v>
+        <v>0.089s</v>
       </c>
       <c r="M10" t="str">
         <v>N/A</v>
@@ -992,7 +992,7 @@
         <v>PASS</v>
       </c>
       <c r="L11" t="str">
-        <v>0.079s</v>
+        <v>0.061s</v>
       </c>
       <c r="M11" t="str">
         <v>N/A</v>
@@ -1035,7 +1035,7 @@
         <v>PASS</v>
       </c>
       <c r="L12" t="str">
-        <v>0.112s</v>
+        <v>0.161s</v>
       </c>
       <c r="M12" t="str">
         <v>N/A</v>
@@ -1078,7 +1078,7 @@
         <v>PASS</v>
       </c>
       <c r="L13" t="str">
-        <v>0.090s</v>
+        <v>0.118s</v>
       </c>
       <c r="M13" t="str">
         <v>N/A</v>
@@ -1121,7 +1121,7 @@
         <v>PASS</v>
       </c>
       <c r="L14" t="str">
-        <v>0.142s</v>
+        <v>0.134s</v>
       </c>
       <c r="M14" t="str">
         <v>N/A</v>
@@ -1164,7 +1164,7 @@
         <v>PASS</v>
       </c>
       <c r="L15" t="str">
-        <v>0.083s</v>
+        <v>0.062s</v>
       </c>
       <c r="M15" t="str">
         <v>N/A</v>
@@ -1207,7 +1207,7 @@
         <v>PASS</v>
       </c>
       <c r="L16" t="str">
-        <v>0.133s</v>
+        <v>0.111s</v>
       </c>
       <c r="M16" t="str">
         <v>N/A</v>
@@ -1250,7 +1250,7 @@
         <v>PASS</v>
       </c>
       <c r="L17" t="str">
-        <v>0.184s</v>
+        <v>0.156s</v>
       </c>
       <c r="M17" t="str">
         <v>N/A</v>
@@ -1293,7 +1293,7 @@
         <v>PASS</v>
       </c>
       <c r="L18" t="str">
-        <v>0.152s</v>
+        <v>0.142s</v>
       </c>
       <c r="M18" t="str">
         <v>N/A</v>
@@ -1336,7 +1336,7 @@
         <v>PASS</v>
       </c>
       <c r="L19" t="str">
-        <v>0.177s</v>
+        <v>0.079s</v>
       </c>
       <c r="M19" t="str">
         <v>N/A</v>
@@ -1379,7 +1379,7 @@
         <v>PASS</v>
       </c>
       <c r="L20" t="str">
-        <v>0.078s</v>
+        <v>0.104s</v>
       </c>
       <c r="M20" t="str">
         <v>N/A</v>
@@ -1422,7 +1422,7 @@
         <v>PASS</v>
       </c>
       <c r="L21" t="str">
-        <v>0.187s</v>
+        <v>0.182s</v>
       </c>
       <c r="M21" t="str">
         <v>N/A</v>
@@ -1465,7 +1465,7 @@
         <v>PASS</v>
       </c>
       <c r="L22" t="str">
-        <v>0.117s</v>
+        <v>0.143s</v>
       </c>
       <c r="M22" t="str">
         <v>N/A</v>
@@ -1508,7 +1508,7 @@
         <v>PASS</v>
       </c>
       <c r="L23" t="str">
-        <v>0.088s</v>
+        <v>0.147s</v>
       </c>
       <c r="M23" t="str">
         <v>N/A</v>
@@ -1551,7 +1551,7 @@
         <v>PASS</v>
       </c>
       <c r="L24" t="str">
-        <v>0.056s</v>
+        <v>0.081s</v>
       </c>
       <c r="M24" t="str">
         <v>N/A</v>
@@ -1594,7 +1594,7 @@
         <v>PASS</v>
       </c>
       <c r="L25" t="str">
-        <v>0.128s</v>
+        <v>0.172s</v>
       </c>
       <c r="M25" t="str">
         <v>N/A</v>
@@ -1637,7 +1637,7 @@
         <v>PASS</v>
       </c>
       <c r="L26" t="str">
-        <v>0.100s</v>
+        <v>0.053s</v>
       </c>
       <c r="M26" t="str">
         <v>N/A</v>
@@ -1680,7 +1680,7 @@
         <v>PASS</v>
       </c>
       <c r="L27" t="str">
-        <v>0.066s</v>
+        <v>0.060s</v>
       </c>
       <c r="M27" t="str">
         <v>N/A</v>
@@ -1723,7 +1723,7 @@
         <v>PASS</v>
       </c>
       <c r="L28" t="str">
-        <v>0.141s</v>
+        <v>0.069s</v>
       </c>
       <c r="M28" t="str">
         <v>N/A</v>
@@ -1766,7 +1766,7 @@
         <v>PASS</v>
       </c>
       <c r="L29" t="str">
-        <v>0.087s</v>
+        <v>0.066s</v>
       </c>
       <c r="M29" t="str">
         <v>N/A</v>
@@ -1809,7 +1809,7 @@
         <v>PASS</v>
       </c>
       <c r="L30" t="str">
-        <v>0.055s</v>
+        <v>0.172s</v>
       </c>
       <c r="M30" t="str">
         <v>N/A</v>
@@ -1852,7 +1852,7 @@
         <v>PASS</v>
       </c>
       <c r="L31" t="str">
-        <v>0.135s</v>
+        <v>0.066s</v>
       </c>
       <c r="M31" t="str">
         <v>N/A</v>
@@ -1895,7 +1895,7 @@
         <v>PASS</v>
       </c>
       <c r="L32" t="str">
-        <v>0.148s</v>
+        <v>0.160s</v>
       </c>
       <c r="M32" t="str">
         <v>N/A</v>
@@ -1981,7 +1981,7 @@
         <v>PASS</v>
       </c>
       <c r="L34" t="str">
-        <v>0.090s</v>
+        <v>0.107s</v>
       </c>
       <c r="M34" t="str">
         <v>N/A</v>
@@ -2024,7 +2024,7 @@
         <v>PASS</v>
       </c>
       <c r="L35" t="str">
-        <v>0.150s</v>
+        <v>0.136s</v>
       </c>
       <c r="M35" t="str">
         <v>N/A</v>
@@ -2067,7 +2067,7 @@
         <v>PASS</v>
       </c>
       <c r="L36" t="str">
-        <v>0.076s</v>
+        <v>0.149s</v>
       </c>
       <c r="M36" t="str">
         <v>N/A</v>
@@ -2110,7 +2110,7 @@
         <v>PASS</v>
       </c>
       <c r="L37" t="str">
-        <v>0.184s</v>
+        <v>0.154s</v>
       </c>
       <c r="M37" t="str">
         <v>N/A</v>
@@ -2153,7 +2153,7 @@
         <v>PASS</v>
       </c>
       <c r="L38" t="str">
-        <v>0.152s</v>
+        <v>0.050s</v>
       </c>
       <c r="M38" t="str">
         <v>N/A</v>
@@ -2196,7 +2196,7 @@
         <v>PASS</v>
       </c>
       <c r="L39" t="str">
-        <v>0.069s</v>
+        <v>0.175s</v>
       </c>
       <c r="M39" t="str">
         <v>N/A</v>
@@ -2239,7 +2239,7 @@
         <v>PASS</v>
       </c>
       <c r="L40" t="str">
-        <v>0.055s</v>
+        <v>0.189s</v>
       </c>
       <c r="M40" t="str">
         <v>N/A</v>
@@ -2282,7 +2282,7 @@
         <v>PASS</v>
       </c>
       <c r="L41" t="str">
-        <v>0.067s</v>
+        <v>0.128s</v>
       </c>
       <c r="M41" t="str">
         <v>N/A</v>
@@ -2325,7 +2325,7 @@
         <v>PASS</v>
       </c>
       <c r="L42" t="str">
-        <v>0.120s</v>
+        <v>0.156s</v>
       </c>
       <c r="M42" t="str">
         <v>N/A</v>
@@ -2368,7 +2368,7 @@
         <v>PASS</v>
       </c>
       <c r="L43" t="str">
-        <v>0.112s</v>
+        <v>0.053s</v>
       </c>
       <c r="M43" t="str">
         <v>N/A</v>
@@ -2411,7 +2411,7 @@
         <v>PASS</v>
       </c>
       <c r="L44" t="str">
-        <v>0.097s</v>
+        <v>0.058s</v>
       </c>
       <c r="M44" t="str">
         <v>N/A</v>
@@ -2454,7 +2454,7 @@
         <v>PASS</v>
       </c>
       <c r="L45" t="str">
-        <v>0.083s</v>
+        <v>0.105s</v>
       </c>
       <c r="M45" t="str">
         <v>N/A</v>
@@ -2497,7 +2497,7 @@
         <v>PASS</v>
       </c>
       <c r="L46" t="str">
-        <v>0.164s</v>
+        <v>0.181s</v>
       </c>
       <c r="M46" t="str">
         <v>N/A</v>
@@ -2540,7 +2540,7 @@
         <v>PASS</v>
       </c>
       <c r="L47" t="str">
-        <v>0.091s</v>
+        <v>0.078s</v>
       </c>
       <c r="M47" t="str">
         <v>N/A</v>
@@ -2583,7 +2583,7 @@
         <v>PASS</v>
       </c>
       <c r="L48" t="str">
-        <v>0.081s</v>
+        <v>0.160s</v>
       </c>
       <c r="M48" t="str">
         <v>N/A</v>
@@ -2626,7 +2626,7 @@
         <v>PASS</v>
       </c>
       <c r="L49" t="str">
-        <v>0.104s</v>
+        <v>0.163s</v>
       </c>
       <c r="M49" t="str">
         <v>N/A</v>
@@ -2669,7 +2669,7 @@
         <v>PASS</v>
       </c>
       <c r="L50" t="str">
-        <v>0.054s</v>
+        <v>0.053s</v>
       </c>
       <c r="M50" t="str">
         <v>N/A</v>
@@ -2712,7 +2712,7 @@
         <v>PASS</v>
       </c>
       <c r="L51" t="str">
-        <v>0.156s</v>
+        <v>0.182s</v>
       </c>
       <c r="M51" t="str">
         <v>N/A</v>
@@ -2755,7 +2755,7 @@
         <v>PASS</v>
       </c>
       <c r="L52" t="str">
-        <v>0.051s</v>
+        <v>0.114s</v>
       </c>
       <c r="M52" t="str">
         <v>N/A</v>
@@ -2798,7 +2798,7 @@
         <v>PASS</v>
       </c>
       <c r="L53" t="str">
-        <v>0.121s</v>
+        <v>0.162s</v>
       </c>
       <c r="M53" t="str">
         <v>N/A</v>
@@ -2841,7 +2841,7 @@
         <v>PASS</v>
       </c>
       <c r="L54" t="str">
-        <v>0.121s</v>
+        <v>0.157s</v>
       </c>
       <c r="M54" t="str">
         <v>N/A</v>
@@ -2884,7 +2884,7 @@
         <v>PASS</v>
       </c>
       <c r="L55" t="str">
-        <v>0.051s</v>
+        <v>0.103s</v>
       </c>
       <c r="M55" t="str">
         <v>N/A</v>
@@ -2927,7 +2927,7 @@
         <v>PASS</v>
       </c>
       <c r="L56" t="str">
-        <v>0.168s</v>
+        <v>0.108s</v>
       </c>
       <c r="M56" t="str">
         <v>N/A</v>
@@ -2970,7 +2970,7 @@
         <v>PASS</v>
       </c>
       <c r="L57" t="str">
-        <v>0.058s</v>
+        <v>0.101s</v>
       </c>
       <c r="M57" t="str">
         <v>N/A</v>
@@ -3013,7 +3013,7 @@
         <v>PASS</v>
       </c>
       <c r="L58" t="str">
-        <v>0.062s</v>
+        <v>0.094s</v>
       </c>
       <c r="M58" t="str">
         <v>N/A</v>
@@ -3056,7 +3056,7 @@
         <v>PASS</v>
       </c>
       <c r="L59" t="str">
-        <v>0.103s</v>
+        <v>0.063s</v>
       </c>
       <c r="M59" t="str">
         <v>N/A</v>
@@ -3099,7 +3099,7 @@
         <v>PASS</v>
       </c>
       <c r="L60" t="str">
-        <v>0.147s</v>
+        <v>0.163s</v>
       </c>
       <c r="M60" t="str">
         <v>N/A</v>
@@ -3142,7 +3142,7 @@
         <v>PASS</v>
       </c>
       <c r="L61" t="str">
-        <v>0.153s</v>
+        <v>0.084s</v>
       </c>
       <c r="M61" t="str">
         <v>N/A</v>
@@ -3185,7 +3185,7 @@
         <v>PASS</v>
       </c>
       <c r="L62" t="str">
-        <v>0.145s</v>
+        <v>0.110s</v>
       </c>
       <c r="M62" t="str">
         <v>N/A</v>
@@ -3228,7 +3228,7 @@
         <v>PASS</v>
       </c>
       <c r="L63" t="str">
-        <v>0.060s</v>
+        <v>0.088s</v>
       </c>
       <c r="M63" t="str">
         <v>N/A</v>
@@ -3271,7 +3271,7 @@
         <v>PASS</v>
       </c>
       <c r="L64" t="str">
-        <v>0.110s</v>
+        <v>0.135s</v>
       </c>
       <c r="M64" t="str">
         <v>N/A</v>
@@ -3314,7 +3314,7 @@
         <v>PASS</v>
       </c>
       <c r="L65" t="str">
-        <v>0.127s</v>
+        <v>0.166s</v>
       </c>
       <c r="M65" t="str">
         <v>N/A</v>
@@ -3357,7 +3357,7 @@
         <v>PASS</v>
       </c>
       <c r="L66" t="str">
-        <v>0.109s</v>
+        <v>0.100s</v>
       </c>
       <c r="M66" t="str">
         <v>N/A</v>
@@ -3400,7 +3400,7 @@
         <v>PASS</v>
       </c>
       <c r="L67" t="str">
-        <v>0.108s</v>
+        <v>0.078s</v>
       </c>
       <c r="M67" t="str">
         <v>N/A</v>
@@ -3443,7 +3443,7 @@
         <v>PASS</v>
       </c>
       <c r="L68" t="str">
-        <v>0.132s</v>
+        <v>0.081s</v>
       </c>
       <c r="M68" t="str">
         <v>N/A</v>
@@ -3486,7 +3486,7 @@
         <v>PASS</v>
       </c>
       <c r="L69" t="str">
-        <v>0.065s</v>
+        <v>0.051s</v>
       </c>
       <c r="M69" t="str">
         <v>N/A</v>
@@ -3529,7 +3529,7 @@
         <v>PASS</v>
       </c>
       <c r="L70" t="str">
-        <v>0.097s</v>
+        <v>0.052s</v>
       </c>
       <c r="M70" t="str">
         <v>N/A</v>
@@ -3572,7 +3572,7 @@
         <v>PASS</v>
       </c>
       <c r="L71" t="str">
-        <v>0.120s</v>
+        <v>0.131s</v>
       </c>
       <c r="M71" t="str">
         <v>N/A</v>
@@ -3615,7 +3615,7 @@
         <v>PASS</v>
       </c>
       <c r="L72" t="str">
-        <v>0.123s</v>
+        <v>0.058s</v>
       </c>
       <c r="M72" t="str">
         <v>N/A</v>
@@ -3658,7 +3658,7 @@
         <v>PASS</v>
       </c>
       <c r="L73" t="str">
-        <v>0.172s</v>
+        <v>0.184s</v>
       </c>
       <c r="M73" t="str">
         <v>N/A</v>
@@ -3701,7 +3701,7 @@
         <v>PASS</v>
       </c>
       <c r="L74" t="str">
-        <v>0.068s</v>
+        <v>0.058s</v>
       </c>
       <c r="M74" t="str">
         <v>N/A</v>
@@ -3744,7 +3744,7 @@
         <v>PASS</v>
       </c>
       <c r="L75" t="str">
-        <v>0.066s</v>
+        <v>0.095s</v>
       </c>
       <c r="M75" t="str">
         <v>N/A</v>
@@ -3787,7 +3787,7 @@
         <v>PASS</v>
       </c>
       <c r="L76" t="str">
-        <v>0.163s</v>
+        <v>0.055s</v>
       </c>
       <c r="M76" t="str">
         <v>N/A</v>
@@ -3830,7 +3830,7 @@
         <v>PASS</v>
       </c>
       <c r="L77" t="str">
-        <v>0.177s</v>
+        <v>0.061s</v>
       </c>
       <c r="M77" t="str">
         <v>N/A</v>
@@ -3873,7 +3873,7 @@
         <v>PASS</v>
       </c>
       <c r="L78" t="str">
-        <v>0.050s</v>
+        <v>0.162s</v>
       </c>
       <c r="M78" t="str">
         <v>N/A</v>
@@ -3916,7 +3916,7 @@
         <v>PASS</v>
       </c>
       <c r="L79" t="str">
-        <v>0.086s</v>
+        <v>0.156s</v>
       </c>
       <c r="M79" t="str">
         <v>N/A</v>
@@ -3959,7 +3959,7 @@
         <v>PASS</v>
       </c>
       <c r="L80" t="str">
-        <v>0.117s</v>
+        <v>0.054s</v>
       </c>
       <c r="M80" t="str">
         <v>N/A</v>
@@ -4002,7 +4002,7 @@
         <v>PASS</v>
       </c>
       <c r="L81" t="str">
-        <v>0.090s</v>
+        <v>0.074s</v>
       </c>
       <c r="M81" t="str">
         <v>N/A</v>
@@ -4045,7 +4045,7 @@
         <v>PASS</v>
       </c>
       <c r="L82" t="str">
-        <v>0.062s</v>
+        <v>0.147s</v>
       </c>
       <c r="M82" t="str">
         <v>N/A</v>
@@ -4088,7 +4088,7 @@
         <v>PASS</v>
       </c>
       <c r="L83" t="str">
-        <v>0.081s</v>
+        <v>0.084s</v>
       </c>
       <c r="M83" t="str">
         <v>N/A</v>
@@ -4131,7 +4131,7 @@
         <v>PASS</v>
       </c>
       <c r="L84" t="str">
-        <v>0.162s</v>
+        <v>0.116s</v>
       </c>
       <c r="M84" t="str">
         <v>N/A</v>
@@ -4174,7 +4174,7 @@
         <v>PASS</v>
       </c>
       <c r="L85" t="str">
-        <v>0.168s</v>
+        <v>0.067s</v>
       </c>
       <c r="M85" t="str">
         <v>N/A</v>
@@ -4217,7 +4217,7 @@
         <v>PASS</v>
       </c>
       <c r="L86" t="str">
-        <v>0.122s</v>
+        <v>0.072s</v>
       </c>
       <c r="M86" t="str">
         <v>N/A</v>
@@ -4260,7 +4260,7 @@
         <v>PASS</v>
       </c>
       <c r="L87" t="str">
-        <v>0.074s</v>
+        <v>0.111s</v>
       </c>
       <c r="M87" t="str">
         <v>N/A</v>
@@ -4303,7 +4303,7 @@
         <v>PASS</v>
       </c>
       <c r="L88" t="str">
-        <v>0.074s</v>
+        <v>0.080s</v>
       </c>
       <c r="M88" t="str">
         <v>N/A</v>
@@ -4346,7 +4346,7 @@
         <v>PASS</v>
       </c>
       <c r="L89" t="str">
-        <v>0.073s</v>
+        <v>0.060s</v>
       </c>
       <c r="M89" t="str">
         <v>N/A</v>
@@ -4389,7 +4389,7 @@
         <v>PASS</v>
       </c>
       <c r="L90" t="str">
-        <v>0.128s</v>
+        <v>0.181s</v>
       </c>
       <c r="M90" t="str">
         <v>N/A</v>
@@ -4432,7 +4432,7 @@
         <v>PASS</v>
       </c>
       <c r="L91" t="str">
-        <v>0.175s</v>
+        <v>0.113s</v>
       </c>
       <c r="M91" t="str">
         <v>N/A</v>
@@ -4475,7 +4475,7 @@
         <v>PASS</v>
       </c>
       <c r="L92" t="str">
-        <v>0.126s</v>
+        <v>0.164s</v>
       </c>
       <c r="M92" t="str">
         <v>N/A</v>
@@ -4518,7 +4518,7 @@
         <v>PASS</v>
       </c>
       <c r="L93" t="str">
-        <v>0.168s</v>
+        <v>0.123s</v>
       </c>
       <c r="M93" t="str">
         <v>N/A</v>
@@ -4561,7 +4561,7 @@
         <v>PASS</v>
       </c>
       <c r="L94" t="str">
-        <v>0.139s</v>
+        <v>0.145s</v>
       </c>
       <c r="M94" t="str">
         <v>N/A</v>
@@ -4604,7 +4604,7 @@
         <v>PASS</v>
       </c>
       <c r="L95" t="str">
-        <v>0.099s</v>
+        <v>0.093s</v>
       </c>
       <c r="M95" t="str">
         <v>N/A</v>
@@ -4647,7 +4647,7 @@
         <v>PASS</v>
       </c>
       <c r="L96" t="str">
-        <v>0.155s</v>
+        <v>0.132s</v>
       </c>
       <c r="M96" t="str">
         <v>N/A</v>
@@ -4690,7 +4690,7 @@
         <v>PASS</v>
       </c>
       <c r="L97" t="str">
-        <v>0.131s</v>
+        <v>0.142s</v>
       </c>
       <c r="M97" t="str">
         <v>N/A</v>
@@ -4733,7 +4733,7 @@
         <v>PASS</v>
       </c>
       <c r="L98" t="str">
-        <v>0.150s</v>
+        <v>0.140s</v>
       </c>
       <c r="M98" t="str">
         <v>N/A</v>
@@ -4776,7 +4776,7 @@
         <v>PASS</v>
       </c>
       <c r="L99" t="str">
-        <v>0.186s</v>
+        <v>0.167s</v>
       </c>
       <c r="M99" t="str">
         <v>N/A</v>
@@ -4819,7 +4819,7 @@
         <v>PASS</v>
       </c>
       <c r="L100" t="str">
-        <v>0.175s</v>
+        <v>0.051s</v>
       </c>
       <c r="M100" t="str">
         <v>N/A</v>
@@ -4862,7 +4862,7 @@
         <v>PASS</v>
       </c>
       <c r="L101" t="str">
-        <v>0.078s</v>
+        <v>0.162s</v>
       </c>
       <c r="M101" t="str">
         <v>N/A</v>
@@ -4905,7 +4905,7 @@
         <v>PASS</v>
       </c>
       <c r="L102" t="str">
-        <v>0.142s</v>
+        <v>0.184s</v>
       </c>
       <c r="M102" t="str">
         <v>N/A</v>
@@ -4948,7 +4948,7 @@
         <v>PASS</v>
       </c>
       <c r="L103" t="str">
-        <v>0.094s</v>
+        <v>0.124s</v>
       </c>
       <c r="M103" t="str">
         <v>N/A</v>
@@ -4991,7 +4991,7 @@
         <v>PASS</v>
       </c>
       <c r="L104" t="str">
-        <v>0.095s</v>
+        <v>0.057s</v>
       </c>
       <c r="M104" t="str">
         <v>N/A</v>
@@ -5034,7 +5034,7 @@
         <v>PASS</v>
       </c>
       <c r="L105" t="str">
-        <v>0.089s</v>
+        <v>0.059s</v>
       </c>
       <c r="M105" t="str">
         <v>N/A</v>
@@ -5077,7 +5077,7 @@
         <v>PASS</v>
       </c>
       <c r="L106" t="str">
-        <v>0.097s</v>
+        <v>0.067s</v>
       </c>
       <c r="M106" t="str">
         <v>N/A</v>
@@ -5120,7 +5120,7 @@
         <v>PASS</v>
       </c>
       <c r="L107" t="str">
-        <v>0.076s</v>
+        <v>0.092s</v>
       </c>
       <c r="M107" t="str">
         <v>N/A</v>
@@ -5163,7 +5163,7 @@
         <v>PASS</v>
       </c>
       <c r="L108" t="str">
-        <v>0.122s</v>
+        <v>0.100s</v>
       </c>
       <c r="M108" t="str">
         <v>N/A</v>
@@ -5206,7 +5206,7 @@
         <v>PASS</v>
       </c>
       <c r="L109" t="str">
-        <v>0.097s</v>
+        <v>0.179s</v>
       </c>
       <c r="M109" t="str">
         <v>N/A</v>
@@ -5249,7 +5249,7 @@
         <v>PASS</v>
       </c>
       <c r="L110" t="str">
-        <v>0.150s</v>
+        <v>0.055s</v>
       </c>
       <c r="M110" t="str">
         <v>N/A</v>
@@ -5292,7 +5292,7 @@
         <v>PASS</v>
       </c>
       <c r="L111" t="str">
-        <v>0.085s</v>
+        <v>0.181s</v>
       </c>
       <c r="M111" t="str">
         <v>N/A</v>
@@ -5335,7 +5335,7 @@
         <v>PASS</v>
       </c>
       <c r="L112" t="str">
-        <v>0.086s</v>
+        <v>0.139s</v>
       </c>
       <c r="M112" t="str">
         <v>N/A</v>
@@ -5378,7 +5378,7 @@
         <v>PASS</v>
       </c>
       <c r="L113" t="str">
-        <v>0.109s</v>
+        <v>0.142s</v>
       </c>
       <c r="M113" t="str">
         <v>N/A</v>
@@ -5421,7 +5421,7 @@
         <v>PASS</v>
       </c>
       <c r="L114" t="str">
-        <v>0.168s</v>
+        <v>0.079s</v>
       </c>
       <c r="M114" t="str">
         <v>N/A</v>
@@ -5464,7 +5464,7 @@
         <v>PASS</v>
       </c>
       <c r="L115" t="str">
-        <v>0.188s</v>
+        <v>0.096s</v>
       </c>
       <c r="M115" t="str">
         <v>N/A</v>
@@ -5507,7 +5507,7 @@
         <v>PASS</v>
       </c>
       <c r="L116" t="str">
-        <v>0.121s</v>
+        <v>0.112s</v>
       </c>
       <c r="M116" t="str">
         <v>N/A</v>
@@ -5550,7 +5550,7 @@
         <v>PASS</v>
       </c>
       <c r="L117" t="str">
-        <v>0.167s</v>
+        <v>0.134s</v>
       </c>
       <c r="M117" t="str">
         <v>N/A</v>
@@ -5593,7 +5593,7 @@
         <v>PASS</v>
       </c>
       <c r="L118" t="str">
-        <v>0.063s</v>
+        <v>0.158s</v>
       </c>
       <c r="M118" t="str">
         <v>N/A</v>
@@ -5636,7 +5636,7 @@
         <v>PASS</v>
       </c>
       <c r="L119" t="str">
-        <v>0.166s</v>
+        <v>0.137s</v>
       </c>
       <c r="M119" t="str">
         <v>N/A</v>
@@ -5679,7 +5679,7 @@
         <v>PASS</v>
       </c>
       <c r="L120" t="str">
-        <v>0.069s</v>
+        <v>0.059s</v>
       </c>
       <c r="M120" t="str">
         <v>N/A</v>
@@ -5722,7 +5722,7 @@
         <v>PASS</v>
       </c>
       <c r="L121" t="str">
-        <v>0.109s</v>
+        <v>0.079s</v>
       </c>
       <c r="M121" t="str">
         <v>N/A</v>
@@ -5765,7 +5765,7 @@
         <v>PASS</v>
       </c>
       <c r="L122" t="str">
-        <v>0.097s</v>
+        <v>0.051s</v>
       </c>
       <c r="M122" t="str">
         <v>N/A</v>
@@ -5808,7 +5808,7 @@
         <v>PASS</v>
       </c>
       <c r="L123" t="str">
-        <v>0.187s</v>
+        <v>0.064s</v>
       </c>
       <c r="M123" t="str">
         <v>N/A</v>
@@ -5851,7 +5851,7 @@
         <v>PASS</v>
       </c>
       <c r="L124" t="str">
-        <v>0.099s</v>
+        <v>0.176s</v>
       </c>
       <c r="M124" t="str">
         <v>N/A</v>
@@ -5894,7 +5894,7 @@
         <v>PASS</v>
       </c>
       <c r="L125" t="str">
-        <v>0.132s</v>
+        <v>0.126s</v>
       </c>
       <c r="M125" t="str">
         <v>N/A</v>
@@ -5937,7 +5937,7 @@
         <v>PASS</v>
       </c>
       <c r="L126" t="str">
-        <v>0.177s</v>
+        <v>0.092s</v>
       </c>
       <c r="M126" t="str">
         <v>N/A</v>
@@ -5980,7 +5980,7 @@
         <v>PASS</v>
       </c>
       <c r="L127" t="str">
-        <v>0.076s</v>
+        <v>0.086s</v>
       </c>
       <c r="M127" t="str">
         <v>N/A</v>
@@ -6023,7 +6023,7 @@
         <v>PASS</v>
       </c>
       <c r="L128" t="str">
-        <v>0.184s</v>
+        <v>0.113s</v>
       </c>
       <c r="M128" t="str">
         <v>N/A</v>
@@ -6066,7 +6066,7 @@
         <v>PASS</v>
       </c>
       <c r="L129" t="str">
-        <v>0.169s</v>
+        <v>0.064s</v>
       </c>
       <c r="M129" t="str">
         <v>N/A</v>
@@ -6109,7 +6109,7 @@
         <v>PASS</v>
       </c>
       <c r="L130" t="str">
-        <v>0.108s</v>
+        <v>0.176s</v>
       </c>
       <c r="M130" t="str">
         <v>N/A</v>
@@ -6152,7 +6152,7 @@
         <v>PASS</v>
       </c>
       <c r="L131" t="str">
-        <v>0.156s</v>
+        <v>0.132s</v>
       </c>
       <c r="M131" t="str">
         <v>N/A</v>
@@ -6195,7 +6195,7 @@
         <v>PASS</v>
       </c>
       <c r="L132" t="str">
-        <v>0.153s</v>
+        <v>0.161s</v>
       </c>
       <c r="M132" t="str">
         <v>N/A</v>
@@ -6238,7 +6238,7 @@
         <v>PASS</v>
       </c>
       <c r="L133" t="str">
-        <v>0.076s</v>
+        <v>0.124s</v>
       </c>
       <c r="M133" t="str">
         <v>N/A</v>
@@ -6281,7 +6281,7 @@
         <v>PASS</v>
       </c>
       <c r="L134" t="str">
-        <v>0.113s</v>
+        <v>0.175s</v>
       </c>
       <c r="M134" t="str">
         <v>N/A</v>
@@ -6324,7 +6324,7 @@
         <v>PASS</v>
       </c>
       <c r="L135" t="str">
-        <v>0.134s</v>
+        <v>0.153s</v>
       </c>
       <c r="M135" t="str">
         <v>N/A</v>
@@ -6367,7 +6367,7 @@
         <v>PASS</v>
       </c>
       <c r="L136" t="str">
-        <v>0.185s</v>
+        <v>0.188s</v>
       </c>
       <c r="M136" t="str">
         <v>N/A</v>
@@ -6410,7 +6410,7 @@
         <v>PASS</v>
       </c>
       <c r="L137" t="str">
-        <v>0.166s</v>
+        <v>0.137s</v>
       </c>
       <c r="M137" t="str">
         <v>N/A</v>
@@ -6453,7 +6453,7 @@
         <v>PASS</v>
       </c>
       <c r="L138" t="str">
-        <v>0.102s</v>
+        <v>0.077s</v>
       </c>
       <c r="M138" t="str">
         <v>N/A</v>
@@ -6496,7 +6496,7 @@
         <v>PASS</v>
       </c>
       <c r="L139" t="str">
-        <v>0.136s</v>
+        <v>0.076s</v>
       </c>
       <c r="M139" t="str">
         <v>N/A</v>
@@ -6539,7 +6539,7 @@
         <v>PASS</v>
       </c>
       <c r="L140" t="str">
-        <v>0.173s</v>
+        <v>0.178s</v>
       </c>
       <c r="M140" t="str">
         <v>N/A</v>
@@ -6582,7 +6582,7 @@
         <v>PASS</v>
       </c>
       <c r="L141" t="str">
-        <v>0.085s</v>
+        <v>0.131s</v>
       </c>
       <c r="M141" t="str">
         <v>N/A</v>
@@ -6625,7 +6625,7 @@
         <v>PASS</v>
       </c>
       <c r="L142" t="str">
-        <v>0.072s</v>
+        <v>0.054s</v>
       </c>
       <c r="M142" t="str">
         <v>N/A</v>
@@ -6668,7 +6668,7 @@
         <v>PASS</v>
       </c>
       <c r="L143" t="str">
-        <v>0.051s</v>
+        <v>0.103s</v>
       </c>
       <c r="M143" t="str">
         <v>N/A</v>
@@ -6711,7 +6711,7 @@
         <v>PASS</v>
       </c>
       <c r="L144" t="str">
-        <v>0.110s</v>
+        <v>0.100s</v>
       </c>
       <c r="M144" t="str">
         <v>N/A</v>
@@ -6754,7 +6754,7 @@
         <v>PASS</v>
       </c>
       <c r="L145" t="str">
-        <v>0.110s</v>
+        <v>0.171s</v>
       </c>
       <c r="M145" t="str">
         <v>N/A</v>
@@ -6797,7 +6797,7 @@
         <v>PASS</v>
       </c>
       <c r="L146" t="str">
-        <v>0.077s</v>
+        <v>0.135s</v>
       </c>
       <c r="M146" t="str">
         <v>N/A</v>
@@ -6840,7 +6840,7 @@
         <v>PASS</v>
       </c>
       <c r="L147" t="str">
-        <v>0.116s</v>
+        <v>0.133s</v>
       </c>
       <c r="M147" t="str">
         <v>N/A</v>
@@ -6883,7 +6883,7 @@
         <v>PASS</v>
       </c>
       <c r="L148" t="str">
-        <v>0.188s</v>
+        <v>0.184s</v>
       </c>
       <c r="M148" t="str">
         <v>N/A</v>
@@ -6926,7 +6926,7 @@
         <v>PASS</v>
       </c>
       <c r="L149" t="str">
-        <v>0.084s</v>
+        <v>0.082s</v>
       </c>
       <c r="M149" t="str">
         <v>N/A</v>
@@ -6969,7 +6969,7 @@
         <v>PASS</v>
       </c>
       <c r="L150" t="str">
-        <v>0.069s</v>
+        <v>0.159s</v>
       </c>
       <c r="M150" t="str">
         <v>N/A</v>
@@ -7012,7 +7012,7 @@
         <v>PASS</v>
       </c>
       <c r="L151" t="str">
-        <v>0.134s</v>
+        <v>0.127s</v>
       </c>
       <c r="M151" t="str">
         <v>N/A</v>
@@ -7055,7 +7055,7 @@
         <v>PASS</v>
       </c>
       <c r="L152" t="str">
-        <v>0.077s</v>
+        <v>0.094s</v>
       </c>
       <c r="M152" t="str">
         <v>N/A</v>
@@ -7098,7 +7098,7 @@
         <v>PASS</v>
       </c>
       <c r="L153" t="str">
-        <v>0.095s</v>
+        <v>0.127s</v>
       </c>
       <c r="M153" t="str">
         <v>N/A</v>
@@ -7141,7 +7141,7 @@
         <v>PASS</v>
       </c>
       <c r="L154" t="str">
-        <v>0.130s</v>
+        <v>0.081s</v>
       </c>
       <c r="M154" t="str">
         <v>N/A</v>
@@ -7184,7 +7184,7 @@
         <v>PASS</v>
       </c>
       <c r="L155" t="str">
-        <v>0.098s</v>
+        <v>0.159s</v>
       </c>
       <c r="M155" t="str">
         <v>N/A</v>
@@ -7227,7 +7227,7 @@
         <v>PASS</v>
       </c>
       <c r="L156" t="str">
-        <v>0.087s</v>
+        <v>0.119s</v>
       </c>
       <c r="M156" t="str">
         <v>N/A</v>
@@ -7270,7 +7270,7 @@
         <v>PASS</v>
       </c>
       <c r="L157" t="str">
-        <v>0.123s</v>
+        <v>0.062s</v>
       </c>
       <c r="M157" t="str">
         <v>N/A</v>
@@ -7313,7 +7313,7 @@
         <v>PASS</v>
       </c>
       <c r="L158" t="str">
-        <v>0.172s</v>
+        <v>0.190s</v>
       </c>
       <c r="M158" t="str">
         <v>N/A</v>
@@ -7356,7 +7356,7 @@
         <v>PASS</v>
       </c>
       <c r="L159" t="str">
-        <v>0.188s</v>
+        <v>0.120s</v>
       </c>
       <c r="M159" t="str">
         <v>N/A</v>
@@ -7399,7 +7399,7 @@
         <v>PASS</v>
       </c>
       <c r="L160" t="str">
-        <v>0.175s</v>
+        <v>0.105s</v>
       </c>
       <c r="M160" t="str">
         <v>N/A</v>
@@ -7442,7 +7442,7 @@
         <v>PASS</v>
       </c>
       <c r="L161" t="str">
-        <v>0.056s</v>
+        <v>0.086s</v>
       </c>
       <c r="M161" t="str">
         <v>N/A</v>
@@ -7485,7 +7485,7 @@
         <v>PASS</v>
       </c>
       <c r="L162" t="str">
-        <v>0.183s</v>
+        <v>0.079s</v>
       </c>
       <c r="M162" t="str">
         <v>N/A</v>
@@ -7528,7 +7528,7 @@
         <v>PASS</v>
       </c>
       <c r="L163" t="str">
-        <v>0.117s</v>
+        <v>0.058s</v>
       </c>
       <c r="M163" t="str">
         <v>N/A</v>
@@ -7571,7 +7571,7 @@
         <v>PASS</v>
       </c>
       <c r="L164" t="str">
-        <v>0.117s</v>
+        <v>0.080s</v>
       </c>
       <c r="M164" t="str">
         <v>N/A</v>
@@ -7614,7 +7614,7 @@
         <v>PASS</v>
       </c>
       <c r="L165" t="str">
-        <v>0.149s</v>
+        <v>0.075s</v>
       </c>
       <c r="M165" t="str">
         <v>N/A</v>
@@ -7657,7 +7657,7 @@
         <v>PASS</v>
       </c>
       <c r="L166" t="str">
-        <v>0.064s</v>
+        <v>0.143s</v>
       </c>
       <c r="M166" t="str">
         <v>N/A</v>
@@ -7700,7 +7700,7 @@
         <v>PASS</v>
       </c>
       <c r="L167" t="str">
-        <v>0.106s</v>
+        <v>0.123s</v>
       </c>
       <c r="M167" t="str">
         <v>N/A</v>
@@ -7743,7 +7743,7 @@
         <v>PASS</v>
       </c>
       <c r="L168" t="str">
-        <v>0.112s</v>
+        <v>0.080s</v>
       </c>
       <c r="M168" t="str">
         <v>N/A</v>
@@ -7786,7 +7786,7 @@
         <v>PASS</v>
       </c>
       <c r="L169" t="str">
-        <v>0.107s</v>
+        <v>0.069s</v>
       </c>
       <c r="M169" t="str">
         <v>N/A</v>
@@ -7829,7 +7829,7 @@
         <v>PASS</v>
       </c>
       <c r="L170" t="str">
-        <v>0.162s</v>
+        <v>0.155s</v>
       </c>
       <c r="M170" t="str">
         <v>N/A</v>
@@ -7872,7 +7872,7 @@
         <v>PASS</v>
       </c>
       <c r="L171" t="str">
-        <v>0.139s</v>
+        <v>0.123s</v>
       </c>
       <c r="M171" t="str">
         <v>N/A</v>
@@ -7915,7 +7915,7 @@
         <v>PASS</v>
       </c>
       <c r="L172" t="str">
-        <v>0.072s</v>
+        <v>0.186s</v>
       </c>
       <c r="M172" t="str">
         <v>N/A</v>
@@ -7958,7 +7958,7 @@
         <v>PASS</v>
       </c>
       <c r="L173" t="str">
-        <v>0.143s</v>
+        <v>0.145s</v>
       </c>
       <c r="M173" t="str">
         <v>N/A</v>
@@ -8001,7 +8001,7 @@
         <v>PASS</v>
       </c>
       <c r="L174" t="str">
-        <v>0.089s</v>
+        <v>0.070s</v>
       </c>
       <c r="M174" t="str">
         <v>N/A</v>
@@ -8044,7 +8044,7 @@
         <v>PASS</v>
       </c>
       <c r="L175" t="str">
-        <v>0.114s</v>
+        <v>0.074s</v>
       </c>
       <c r="M175" t="str">
         <v>N/A</v>
@@ -8087,7 +8087,7 @@
         <v>PASS</v>
       </c>
       <c r="L176" t="str">
-        <v>0.164s</v>
+        <v>0.071s</v>
       </c>
       <c r="M176" t="str">
         <v>N/A</v>
@@ -8130,7 +8130,7 @@
         <v>PASS</v>
       </c>
       <c r="L177" t="str">
-        <v>0.177s</v>
+        <v>0.100s</v>
       </c>
       <c r="M177" t="str">
         <v>N/A</v>
@@ -8173,7 +8173,7 @@
         <v>PASS</v>
       </c>
       <c r="L178" t="str">
-        <v>0.140s</v>
+        <v>0.141s</v>
       </c>
       <c r="M178" t="str">
         <v>N/A</v>
@@ -8216,7 +8216,7 @@
         <v>PASS</v>
       </c>
       <c r="L179" t="str">
-        <v>0.093s</v>
+        <v>0.123s</v>
       </c>
       <c r="M179" t="str">
         <v>N/A</v>
@@ -8259,7 +8259,7 @@
         <v>PASS</v>
       </c>
       <c r="L180" t="str">
-        <v>0.134s</v>
+        <v>0.072s</v>
       </c>
       <c r="M180" t="str">
         <v>N/A</v>
@@ -8302,7 +8302,7 @@
         <v>PASS</v>
       </c>
       <c r="L181" t="str">
-        <v>0.158s</v>
+        <v>0.094s</v>
       </c>
       <c r="M181" t="str">
         <v>N/A</v>
@@ -8345,7 +8345,7 @@
         <v>PASS</v>
       </c>
       <c r="L182" t="str">
-        <v>0.107s</v>
+        <v>0.057s</v>
       </c>
       <c r="M182" t="str">
         <v>N/A</v>
@@ -8388,7 +8388,7 @@
         <v>PASS</v>
       </c>
       <c r="L183" t="str">
-        <v>0.150s</v>
+        <v>0.143s</v>
       </c>
       <c r="M183" t="str">
         <v>N/A</v>
@@ -8431,7 +8431,7 @@
         <v>PASS</v>
       </c>
       <c r="L184" t="str">
-        <v>0.064s</v>
+        <v>0.095s</v>
       </c>
       <c r="M184" t="str">
         <v>N/A</v>
@@ -8474,7 +8474,7 @@
         <v>PASS</v>
       </c>
       <c r="L185" t="str">
-        <v>0.053s</v>
+        <v>0.164s</v>
       </c>
       <c r="M185" t="str">
         <v>N/A</v>
@@ -8517,7 +8517,7 @@
         <v>PASS</v>
       </c>
       <c r="L186" t="str">
-        <v>0.076s</v>
+        <v>0.117s</v>
       </c>
       <c r="M186" t="str">
         <v>N/A</v>
@@ -8560,7 +8560,7 @@
         <v>PASS</v>
       </c>
       <c r="L187" t="str">
-        <v>0.162s</v>
+        <v>0.072s</v>
       </c>
       <c r="M187" t="str">
         <v>N/A</v>
@@ -8603,7 +8603,7 @@
         <v>PASS</v>
       </c>
       <c r="L188" t="str">
-        <v>0.116s</v>
+        <v>0.079s</v>
       </c>
       <c r="M188" t="str">
         <v>N/A</v>
@@ -8646,7 +8646,7 @@
         <v>PASS</v>
       </c>
       <c r="L189" t="str">
-        <v>0.150s</v>
+        <v>0.065s</v>
       </c>
       <c r="M189" t="str">
         <v>N/A</v>
@@ -8689,7 +8689,7 @@
         <v>PASS</v>
       </c>
       <c r="L190" t="str">
-        <v>0.081s</v>
+        <v>0.172s</v>
       </c>
       <c r="M190" t="str">
         <v>N/A</v>
@@ -8732,7 +8732,7 @@
         <v>PASS</v>
       </c>
       <c r="L191" t="str">
-        <v>0.165s</v>
+        <v>0.141s</v>
       </c>
       <c r="M191" t="str">
         <v>N/A</v>
@@ -8775,7 +8775,7 @@
         <v>PASS</v>
       </c>
       <c r="L192" t="str">
-        <v>0.106s</v>
+        <v>0.186s</v>
       </c>
       <c r="M192" t="str">
         <v>N/A</v>
@@ -8818,7 +8818,7 @@
         <v>PASS</v>
       </c>
       <c r="L193" t="str">
-        <v>0.067s</v>
+        <v>0.156s</v>
       </c>
       <c r="M193" t="str">
         <v>N/A</v>
@@ -8861,7 +8861,7 @@
         <v>PASS</v>
       </c>
       <c r="L194" t="str">
-        <v>0.125s</v>
+        <v>0.053s</v>
       </c>
       <c r="M194" t="str">
         <v>N/A</v>
@@ -8904,7 +8904,7 @@
         <v>PASS</v>
       </c>
       <c r="L195" t="str">
-        <v>0.121s</v>
+        <v>0.155s</v>
       </c>
       <c r="M195" t="str">
         <v>N/A</v>
@@ -8947,7 +8947,7 @@
         <v>PASS</v>
       </c>
       <c r="L196" t="str">
-        <v>0.097s</v>
+        <v>0.120s</v>
       </c>
       <c r="M196" t="str">
         <v>N/A</v>
@@ -8990,7 +8990,7 @@
         <v>PASS</v>
       </c>
       <c r="L197" t="str">
-        <v>0.050s</v>
+        <v>0.136s</v>
       </c>
       <c r="M197" t="str">
         <v>N/A</v>
@@ -9033,7 +9033,7 @@
         <v>PASS</v>
       </c>
       <c r="L198" t="str">
-        <v>0.169s</v>
+        <v>0.128s</v>
       </c>
       <c r="M198" t="str">
         <v>N/A</v>
@@ -9076,7 +9076,7 @@
         <v>PASS</v>
       </c>
       <c r="L199" t="str">
-        <v>0.080s</v>
+        <v>0.093s</v>
       </c>
       <c r="M199" t="str">
         <v>N/A</v>
@@ -9119,7 +9119,7 @@
         <v>PASS</v>
       </c>
       <c r="L200" t="str">
-        <v>0.078s</v>
+        <v>0.188s</v>
       </c>
       <c r="M200" t="str">
         <v>N/A</v>
@@ -9162,7 +9162,7 @@
         <v>PASS</v>
       </c>
       <c r="L201" t="str">
-        <v>0.137s</v>
+        <v>0.083s</v>
       </c>
       <c r="M201" t="str">
         <v>N/A</v>
@@ -9205,7 +9205,7 @@
         <v>PASS</v>
       </c>
       <c r="L202" t="str">
-        <v>0.182s</v>
+        <v>0.186s</v>
       </c>
       <c r="M202" t="str">
         <v>N/A</v>
@@ -9248,7 +9248,7 @@
         <v>PASS</v>
       </c>
       <c r="L203" t="str">
-        <v>0.062s</v>
+        <v>0.187s</v>
       </c>
       <c r="M203" t="str">
         <v>N/A</v>
@@ -9291,7 +9291,7 @@
         <v>PASS</v>
       </c>
       <c r="L204" t="str">
-        <v>0.091s</v>
+        <v>0.182s</v>
       </c>
       <c r="M204" t="str">
         <v>N/A</v>
@@ -9334,7 +9334,7 @@
         <v>PASS</v>
       </c>
       <c r="L205" t="str">
-        <v>0.146s</v>
+        <v>0.164s</v>
       </c>
       <c r="M205" t="str">
         <v>N/A</v>
@@ -9377,7 +9377,7 @@
         <v>PASS</v>
       </c>
       <c r="L206" t="str">
-        <v>0.116s</v>
+        <v>0.102s</v>
       </c>
       <c r="M206" t="str">
         <v>N/A</v>
@@ -9420,7 +9420,7 @@
         <v>PASS</v>
       </c>
       <c r="L207" t="str">
-        <v>0.115s</v>
+        <v>0.100s</v>
       </c>
       <c r="M207" t="str">
         <v>N/A</v>
@@ -9463,7 +9463,7 @@
         <v>PASS</v>
       </c>
       <c r="L208" t="str">
-        <v>0.125s</v>
+        <v>0.109s</v>
       </c>
       <c r="M208" t="str">
         <v>N/A</v>
@@ -9506,7 +9506,7 @@
         <v>PASS</v>
       </c>
       <c r="L209" t="str">
-        <v>0.122s</v>
+        <v>0.126s</v>
       </c>
       <c r="M209" t="str">
         <v>N/A</v>
@@ -9549,7 +9549,7 @@
         <v>PASS</v>
       </c>
       <c r="L210" t="str">
-        <v>0.056s</v>
+        <v>0.180s</v>
       </c>
       <c r="M210" t="str">
         <v>N/A</v>
@@ -9592,7 +9592,7 @@
         <v>PASS</v>
       </c>
       <c r="L211" t="str">
-        <v>0.169s</v>
+        <v>0.095s</v>
       </c>
       <c r="M211" t="str">
         <v>N/A</v>
@@ -9635,7 +9635,7 @@
         <v>PASS</v>
       </c>
       <c r="L212" t="str">
-        <v>0.181s</v>
+        <v>0.144s</v>
       </c>
       <c r="M212" t="str">
         <v>N/A</v>
@@ -9678,7 +9678,7 @@
         <v>PASS</v>
       </c>
       <c r="L213" t="str">
-        <v>0.107s</v>
+        <v>0.126s</v>
       </c>
       <c r="M213" t="str">
         <v>N/A</v>
@@ -9721,7 +9721,7 @@
         <v>PASS</v>
       </c>
       <c r="L214" t="str">
-        <v>0.157s</v>
+        <v>0.159s</v>
       </c>
       <c r="M214" t="str">
         <v>N/A</v>
@@ -9764,7 +9764,7 @@
         <v>PASS</v>
       </c>
       <c r="L215" t="str">
-        <v>0.152s</v>
+        <v>0.081s</v>
       </c>
       <c r="M215" t="str">
         <v>N/A</v>
@@ -9807,7 +9807,7 @@
         <v>PASS</v>
       </c>
       <c r="L216" t="str">
-        <v>0.140s</v>
+        <v>0.121s</v>
       </c>
       <c r="M216" t="str">
         <v>N/A</v>
@@ -9850,7 +9850,7 @@
         <v>PASS</v>
       </c>
       <c r="L217" t="str">
-        <v>0.101s</v>
+        <v>0.111s</v>
       </c>
       <c r="M217" t="str">
         <v>N/A</v>
@@ -9893,7 +9893,7 @@
         <v>PASS</v>
       </c>
       <c r="L218" t="str">
-        <v>0.126s</v>
+        <v>0.174s</v>
       </c>
       <c r="M218" t="str">
         <v>N/A</v>
@@ -9936,7 +9936,7 @@
         <v>PASS</v>
       </c>
       <c r="L219" t="str">
-        <v>0.147s</v>
+        <v>0.184s</v>
       </c>
       <c r="M219" t="str">
         <v>N/A</v>
@@ -9979,7 +9979,7 @@
         <v>PASS</v>
       </c>
       <c r="L220" t="str">
-        <v>0.104s</v>
+        <v>0.085s</v>
       </c>
       <c r="M220" t="str">
         <v>N/A</v>
@@ -10022,7 +10022,7 @@
         <v>PASS</v>
       </c>
       <c r="L221" t="str">
-        <v>0.183s</v>
+        <v>0.169s</v>
       </c>
       <c r="M221" t="str">
         <v>N/A</v>
@@ -10065,7 +10065,7 @@
         <v>PASS</v>
       </c>
       <c r="L222" t="str">
-        <v>0.132s</v>
+        <v>0.102s</v>
       </c>
       <c r="M222" t="str">
         <v>N/A</v>
@@ -10108,7 +10108,7 @@
         <v>PASS</v>
       </c>
       <c r="L223" t="str">
-        <v>0.085s</v>
+        <v>0.156s</v>
       </c>
       <c r="M223" t="str">
         <v>N/A</v>
@@ -10151,7 +10151,7 @@
         <v>PASS</v>
       </c>
       <c r="L224" t="str">
-        <v>0.107s</v>
+        <v>0.095s</v>
       </c>
       <c r="M224" t="str">
         <v>N/A</v>
@@ -10194,7 +10194,7 @@
         <v>PASS</v>
       </c>
       <c r="L225" t="str">
-        <v>0.137s</v>
+        <v>0.124s</v>
       </c>
       <c r="M225" t="str">
         <v>N/A</v>
@@ -10237,7 +10237,7 @@
         <v>PASS</v>
       </c>
       <c r="L226" t="str">
-        <v>0.181s</v>
+        <v>0.088s</v>
       </c>
       <c r="M226" t="str">
         <v>N/A</v>
@@ -10280,7 +10280,7 @@
         <v>PASS</v>
       </c>
       <c r="L227" t="str">
-        <v>0.182s</v>
+        <v>0.097s</v>
       </c>
       <c r="M227" t="str">
         <v>N/A</v>
@@ -10323,7 +10323,7 @@
         <v>PASS</v>
       </c>
       <c r="L228" t="str">
-        <v>0.089s</v>
+        <v>0.188s</v>
       </c>
       <c r="M228" t="str">
         <v>N/A</v>
@@ -10366,7 +10366,7 @@
         <v>PASS</v>
       </c>
       <c r="L229" t="str">
-        <v>0.051s</v>
+        <v>0.103s</v>
       </c>
       <c r="M229" t="str">
         <v>N/A</v>
@@ -10409,7 +10409,7 @@
         <v>PASS</v>
       </c>
       <c r="L230" t="str">
-        <v>0.065s</v>
+        <v>0.051s</v>
       </c>
       <c r="M230" t="str">
         <v>N/A</v>
@@ -10452,7 +10452,7 @@
         <v>PASS</v>
       </c>
       <c r="L231" t="str">
-        <v>0.065s</v>
+        <v>0.053s</v>
       </c>
       <c r="M231" t="str">
         <v>N/A</v>
@@ -10495,7 +10495,7 @@
         <v>PASS</v>
       </c>
       <c r="L232" t="str">
-        <v>0.105s</v>
+        <v>0.188s</v>
       </c>
       <c r="M232" t="str">
         <v>N/A</v>
@@ -10538,7 +10538,7 @@
         <v>PASS</v>
       </c>
       <c r="L233" t="str">
-        <v>0.175s</v>
+        <v>0.053s</v>
       </c>
       <c r="M233" t="str">
         <v>N/A</v>
@@ -10581,7 +10581,7 @@
         <v>PASS</v>
       </c>
       <c r="L234" t="str">
-        <v>0.174s</v>
+        <v>0.076s</v>
       </c>
       <c r="M234" t="str">
         <v>N/A</v>
@@ -10624,7 +10624,7 @@
         <v>PASS</v>
       </c>
       <c r="L235" t="str">
-        <v>0.103s</v>
+        <v>0.142s</v>
       </c>
       <c r="M235" t="str">
         <v>N/A</v>
@@ -10667,7 +10667,7 @@
         <v>PASS</v>
       </c>
       <c r="L236" t="str">
-        <v>0.137s</v>
+        <v>0.139s</v>
       </c>
       <c r="M236" t="str">
         <v>N/A</v>
@@ -10710,7 +10710,7 @@
         <v>PASS</v>
       </c>
       <c r="L237" t="str">
-        <v>0.067s</v>
+        <v>0.128s</v>
       </c>
       <c r="M237" t="str">
         <v>N/A</v>
@@ -10753,7 +10753,7 @@
         <v>PASS</v>
       </c>
       <c r="L238" t="str">
-        <v>0.132s</v>
+        <v>0.127s</v>
       </c>
       <c r="M238" t="str">
         <v>N/A</v>
@@ -10796,7 +10796,7 @@
         <v>PASS</v>
       </c>
       <c r="L239" t="str">
-        <v>0.190s</v>
+        <v>0.156s</v>
       </c>
       <c r="M239" t="str">
         <v>N/A</v>
@@ -10839,7 +10839,7 @@
         <v>PASS</v>
       </c>
       <c r="L240" t="str">
-        <v>0.126s</v>
+        <v>0.137s</v>
       </c>
       <c r="M240" t="str">
         <v>N/A</v>
@@ -10882,7 +10882,7 @@
         <v>PASS</v>
       </c>
       <c r="L241" t="str">
-        <v>0.183s</v>
+        <v>0.056s</v>
       </c>
       <c r="M241" t="str">
         <v>N/A</v>
@@ -10925,7 +10925,7 @@
         <v>PASS</v>
       </c>
       <c r="L242" t="str">
-        <v>0.138s</v>
+        <v>0.159s</v>
       </c>
       <c r="M242" t="str">
         <v>N/A</v>
@@ -10968,7 +10968,7 @@
         <v>PASS</v>
       </c>
       <c r="L243" t="str">
-        <v>0.128s</v>
+        <v>0.094s</v>
       </c>
       <c r="M243" t="str">
         <v>N/A</v>
@@ -11011,7 +11011,7 @@
         <v>PASS</v>
       </c>
       <c r="L244" t="str">
-        <v>0.060s</v>
+        <v>0.064s</v>
       </c>
       <c r="M244" t="str">
         <v>N/A</v>
@@ -11054,7 +11054,7 @@
         <v>PASS</v>
       </c>
       <c r="L245" t="str">
-        <v>0.140s</v>
+        <v>0.064s</v>
       </c>
       <c r="M245" t="str">
         <v>N/A</v>
@@ -11097,7 +11097,7 @@
         <v>PASS</v>
       </c>
       <c r="L246" t="str">
-        <v>0.167s</v>
+        <v>0.190s</v>
       </c>
       <c r="M246" t="str">
         <v>N/A</v>
@@ -11140,7 +11140,7 @@
         <v>PASS</v>
       </c>
       <c r="L247" t="str">
-        <v>0.091s</v>
+        <v>0.165s</v>
       </c>
       <c r="M247" t="str">
         <v>N/A</v>
@@ -11183,7 +11183,7 @@
         <v>PASS</v>
       </c>
       <c r="L248" t="str">
-        <v>0.155s</v>
+        <v>0.113s</v>
       </c>
       <c r="M248" t="str">
         <v>N/A</v>
@@ -11226,7 +11226,7 @@
         <v>PASS</v>
       </c>
       <c r="L249" t="str">
-        <v>0.069s</v>
+        <v>0.170s</v>
       </c>
       <c r="M249" t="str">
         <v>N/A</v>
@@ -11269,7 +11269,7 @@
         <v>PASS</v>
       </c>
       <c r="L250" t="str">
-        <v>0.095s</v>
+        <v>0.165s</v>
       </c>
       <c r="M250" t="str">
         <v>N/A</v>
@@ -11312,7 +11312,7 @@
         <v>PASS</v>
       </c>
       <c r="L251" t="str">
-        <v>0.186s</v>
+        <v>0.082s</v>
       </c>
       <c r="M251" t="str">
         <v>N/A</v>
@@ -11355,7 +11355,7 @@
         <v>PASS</v>
       </c>
       <c r="L252" t="str">
-        <v>0.052s</v>
+        <v>0.125s</v>
       </c>
       <c r="M252" t="str">
         <v>N/A</v>
@@ -11398,7 +11398,7 @@
         <v>PASS</v>
       </c>
       <c r="L253" t="str">
-        <v>0.154s</v>
+        <v>0.158s</v>
       </c>
       <c r="M253" t="str">
         <v>N/A</v>
@@ -11441,7 +11441,7 @@
         <v>PASS</v>
       </c>
       <c r="L254" t="str">
-        <v>0.095s</v>
+        <v>0.158s</v>
       </c>
       <c r="M254" t="str">
         <v>N/A</v>
@@ -11484,7 +11484,7 @@
         <v>PASS</v>
       </c>
       <c r="L255" t="str">
-        <v>0.123s</v>
+        <v>0.146s</v>
       </c>
       <c r="M255" t="str">
         <v>N/A</v>
@@ -11527,7 +11527,7 @@
         <v>PASS</v>
       </c>
       <c r="L256" t="str">
-        <v>0.182s</v>
+        <v>0.173s</v>
       </c>
       <c r="M256" t="str">
         <v>N/A</v>
@@ -11570,7 +11570,7 @@
         <v>PASS</v>
       </c>
       <c r="L257" t="str">
-        <v>0.056s</v>
+        <v>0.051s</v>
       </c>
       <c r="M257" t="str">
         <v>N/A</v>
@@ -11613,7 +11613,7 @@
         <v>PASS</v>
       </c>
       <c r="L258" t="str">
-        <v>0.139s</v>
+        <v>0.074s</v>
       </c>
       <c r="M258" t="str">
         <v>N/A</v>
@@ -11656,7 +11656,7 @@
         <v>PASS</v>
       </c>
       <c r="L259" t="str">
-        <v>0.102s</v>
+        <v>0.100s</v>
       </c>
       <c r="M259" t="str">
         <v>N/A</v>
@@ -11699,7 +11699,7 @@
         <v>PASS</v>
       </c>
       <c r="L260" t="str">
-        <v>0.077s</v>
+        <v>0.101s</v>
       </c>
       <c r="M260" t="str">
         <v>N/A</v>
@@ -11742,7 +11742,7 @@
         <v>PASS</v>
       </c>
       <c r="L261" t="str">
-        <v>0.087s</v>
+        <v>0.058s</v>
       </c>
       <c r="M261" t="str">
         <v>N/A</v>
@@ -11785,7 +11785,7 @@
         <v>PASS</v>
       </c>
       <c r="L262" t="str">
-        <v>0.078s</v>
+        <v>0.104s</v>
       </c>
       <c r="M262" t="str">
         <v>N/A</v>
@@ -11828,7 +11828,7 @@
         <v>PASS</v>
       </c>
       <c r="L263" t="str">
-        <v>0.179s</v>
+        <v>0.160s</v>
       </c>
       <c r="M263" t="str">
         <v>N/A</v>
@@ -11871,7 +11871,7 @@
         <v>PASS</v>
       </c>
       <c r="L264" t="str">
-        <v>0.142s</v>
+        <v>0.163s</v>
       </c>
       <c r="M264" t="str">
         <v>N/A</v>
@@ -11914,7 +11914,7 @@
         <v>PASS</v>
       </c>
       <c r="L265" t="str">
-        <v>0.181s</v>
+        <v>0.093s</v>
       </c>
       <c r="M265" t="str">
         <v>N/A</v>
@@ -11957,7 +11957,7 @@
         <v>PASS</v>
       </c>
       <c r="L266" t="str">
-        <v>0.150s</v>
+        <v>0.152s</v>
       </c>
       <c r="M266" t="str">
         <v>N/A</v>
@@ -12000,7 +12000,7 @@
         <v>PASS</v>
       </c>
       <c r="L267" t="str">
-        <v>0.182s</v>
+        <v>0.084s</v>
       </c>
       <c r="M267" t="str">
         <v>N/A</v>
@@ -12043,7 +12043,7 @@
         <v>PASS</v>
       </c>
       <c r="L268" t="str">
-        <v>0.127s</v>
+        <v>0.187s</v>
       </c>
       <c r="M268" t="str">
         <v>N/A</v>
@@ -12086,7 +12086,7 @@
         <v>PASS</v>
       </c>
       <c r="L269" t="str">
-        <v>0.115s</v>
+        <v>0.064s</v>
       </c>
       <c r="M269" t="str">
         <v>N/A</v>
@@ -12129,7 +12129,7 @@
         <v>PASS</v>
       </c>
       <c r="L270" t="str">
-        <v>0.087s</v>
+        <v>0.092s</v>
       </c>
       <c r="M270" t="str">
         <v>N/A</v>
@@ -12172,7 +12172,7 @@
         <v>PASS</v>
       </c>
       <c r="L271" t="str">
-        <v>0.079s</v>
+        <v>0.137s</v>
       </c>
       <c r="M271" t="str">
         <v>N/A</v>
@@ -12215,7 +12215,7 @@
         <v>PASS</v>
       </c>
       <c r="L272" t="str">
-        <v>0.153s</v>
+        <v>0.070s</v>
       </c>
       <c r="M272" t="str">
         <v>N/A</v>
@@ -12258,7 +12258,7 @@
         <v>PASS</v>
       </c>
       <c r="L273" t="str">
-        <v>0.182s</v>
+        <v>0.154s</v>
       </c>
       <c r="M273" t="str">
         <v>N/A</v>
@@ -12301,7 +12301,7 @@
         <v>PASS</v>
       </c>
       <c r="L274" t="str">
-        <v>0.075s</v>
+        <v>0.135s</v>
       </c>
       <c r="M274" t="str">
         <v>N/A</v>
@@ -12344,7 +12344,7 @@
         <v>PASS</v>
       </c>
       <c r="L275" t="str">
-        <v>0.113s</v>
+        <v>0.120s</v>
       </c>
       <c r="M275" t="str">
         <v>N/A</v>
@@ -12387,7 +12387,7 @@
         <v>PASS</v>
       </c>
       <c r="L276" t="str">
-        <v>0.183s</v>
+        <v>0.177s</v>
       </c>
       <c r="M276" t="str">
         <v>N/A</v>
@@ -12430,7 +12430,7 @@
         <v>PASS</v>
       </c>
       <c r="L277" t="str">
-        <v>0.075s</v>
+        <v>0.065s</v>
       </c>
       <c r="M277" t="str">
         <v>N/A</v>
@@ -12473,7 +12473,7 @@
         <v>PASS</v>
       </c>
       <c r="L278" t="str">
-        <v>0.071s</v>
+        <v>0.172s</v>
       </c>
       <c r="M278" t="str">
         <v>N/A</v>
@@ -12516,7 +12516,7 @@
         <v>PASS</v>
       </c>
       <c r="L279" t="str">
-        <v>0.098s</v>
+        <v>0.089s</v>
       </c>
       <c r="M279" t="str">
         <v>N/A</v>
@@ -12559,7 +12559,7 @@
         <v>PASS</v>
       </c>
       <c r="L280" t="str">
-        <v>0.143s</v>
+        <v>0.091s</v>
       </c>
       <c r="M280" t="str">
         <v>N/A</v>
@@ -12602,7 +12602,7 @@
         <v>PASS</v>
       </c>
       <c r="L281" t="str">
-        <v>0.160s</v>
+        <v>0.146s</v>
       </c>
       <c r="M281" t="str">
         <v>N/A</v>
@@ -12645,7 +12645,7 @@
         <v>PASS</v>
       </c>
       <c r="L282" t="str">
-        <v>0.075s</v>
+        <v>0.158s</v>
       </c>
       <c r="M282" t="str">
         <v>N/A</v>
@@ -12688,7 +12688,7 @@
         <v>PASS</v>
       </c>
       <c r="L283" t="str">
-        <v>0.152s</v>
+        <v>0.122s</v>
       </c>
       <c r="M283" t="str">
         <v>N/A</v>
@@ -12731,7 +12731,7 @@
         <v>PASS</v>
       </c>
       <c r="L284" t="str">
-        <v>0.167s</v>
+        <v>0.157s</v>
       </c>
       <c r="M284" t="str">
         <v>N/A</v>
@@ -12774,7 +12774,7 @@
         <v>PASS</v>
       </c>
       <c r="L285" t="str">
-        <v>0.122s</v>
+        <v>0.167s</v>
       </c>
       <c r="M285" t="str">
         <v>N/A</v>
@@ -12817,7 +12817,7 @@
         <v>PASS</v>
       </c>
       <c r="L286" t="str">
-        <v>0.077s</v>
+        <v>0.113s</v>
       </c>
       <c r="M286" t="str">
         <v>N/A</v>
@@ -12860,7 +12860,7 @@
         <v>PASS</v>
       </c>
       <c r="L287" t="str">
-        <v>0.164s</v>
+        <v>0.096s</v>
       </c>
       <c r="M287" t="str">
         <v>N/A</v>
@@ -12903,7 +12903,7 @@
         <v>PASS</v>
       </c>
       <c r="L288" t="str">
-        <v>0.109s</v>
+        <v>0.076s</v>
       </c>
       <c r="M288" t="str">
         <v>N/A</v>
@@ -12946,7 +12946,7 @@
         <v>PASS</v>
       </c>
       <c r="L289" t="str">
-        <v>0.117s</v>
+        <v>0.143s</v>
       </c>
       <c r="M289" t="str">
         <v>N/A</v>
@@ -12989,7 +12989,7 @@
         <v>PASS</v>
       </c>
       <c r="L290" t="str">
-        <v>0.090s</v>
+        <v>0.159s</v>
       </c>
       <c r="M290" t="str">
         <v>N/A</v>
@@ -13032,7 +13032,7 @@
         <v>PASS</v>
       </c>
       <c r="L291" t="str">
-        <v>0.161s</v>
+        <v>0.188s</v>
       </c>
       <c r="M291" t="str">
         <v>N/A</v>
@@ -13075,7 +13075,7 @@
         <v>PASS</v>
       </c>
       <c r="L292" t="str">
-        <v>0.057s</v>
+        <v>0.059s</v>
       </c>
       <c r="M292" t="str">
         <v>N/A</v>
@@ -13118,7 +13118,7 @@
         <v>PASS</v>
       </c>
       <c r="L293" t="str">
-        <v>0.143s</v>
+        <v>0.123s</v>
       </c>
       <c r="M293" t="str">
         <v>N/A</v>
@@ -13161,7 +13161,7 @@
         <v>PASS</v>
       </c>
       <c r="L294" t="str">
-        <v>0.177s</v>
+        <v>0.167s</v>
       </c>
       <c r="M294" t="str">
         <v>N/A</v>
@@ -13204,7 +13204,7 @@
         <v>PASS</v>
       </c>
       <c r="L295" t="str">
-        <v>0.146s</v>
+        <v>0.131s</v>
       </c>
       <c r="M295" t="str">
         <v>N/A</v>
@@ -13247,7 +13247,7 @@
         <v>PASS</v>
       </c>
       <c r="L296" t="str">
-        <v>0.118s</v>
+        <v>0.064s</v>
       </c>
       <c r="M296" t="str">
         <v>N/A</v>
@@ -13290,7 +13290,7 @@
         <v>PASS</v>
       </c>
       <c r="L297" t="str">
-        <v>0.147s</v>
+        <v>0.171s</v>
       </c>
       <c r="M297" t="str">
         <v>N/A</v>
@@ -13333,7 +13333,7 @@
         <v>PASS</v>
       </c>
       <c r="L298" t="str">
-        <v>0.050s</v>
+        <v>0.159s</v>
       </c>
       <c r="M298" t="str">
         <v>N/A</v>
@@ -13376,7 +13376,7 @@
         <v>PASS</v>
       </c>
       <c r="L299" t="str">
-        <v>0.176s</v>
+        <v>0.102s</v>
       </c>
       <c r="M299" t="str">
         <v>N/A</v>
@@ -13419,7 +13419,7 @@
         <v>PASS</v>
       </c>
       <c r="L300" t="str">
-        <v>0.141s</v>
+        <v>0.133s</v>
       </c>
       <c r="M300" t="str">
         <v>N/A</v>
@@ -13462,7 +13462,7 @@
         <v>PASS</v>
       </c>
       <c r="L301" t="str">
-        <v>0.092s</v>
+        <v>0.056s</v>
       </c>
       <c r="M301" t="str">
         <v>N/A</v>
@@ -13505,7 +13505,7 @@
         <v>PASS</v>
       </c>
       <c r="L302" t="str">
-        <v>0.123s</v>
+        <v>0.136s</v>
       </c>
       <c r="M302" t="str">
         <v>N/A</v>
@@ -13548,7 +13548,7 @@
         <v>PASS</v>
       </c>
       <c r="L303" t="str">
-        <v>0.156s</v>
+        <v>0.169s</v>
       </c>
       <c r="M303" t="str">
         <v>N/A</v>
@@ -13591,7 +13591,7 @@
         <v>PASS</v>
       </c>
       <c r="L304" t="str">
-        <v>0.179s</v>
+        <v>0.054s</v>
       </c>
       <c r="M304" t="str">
         <v>N/A</v>
@@ -13634,7 +13634,7 @@
         <v>PASS</v>
       </c>
       <c r="L305" t="str">
-        <v>0.190s</v>
+        <v>0.102s</v>
       </c>
       <c r="M305" t="str">
         <v>N/A</v>
@@ -13677,7 +13677,7 @@
         <v>PASS</v>
       </c>
       <c r="L306" t="str">
-        <v>0.118s</v>
+        <v>0.079s</v>
       </c>
       <c r="M306" t="str">
         <v>N/A</v>
@@ -13720,7 +13720,7 @@
         <v>PASS</v>
       </c>
       <c r="L307" t="str">
-        <v>0.091s</v>
+        <v>0.093s</v>
       </c>
       <c r="M307" t="str">
         <v>N/A</v>
@@ -13763,7 +13763,7 @@
         <v>PASS</v>
       </c>
       <c r="L308" t="str">
-        <v>0.144s</v>
+        <v>0.142s</v>
       </c>
       <c r="M308" t="str">
         <v>N/A</v>
@@ -13806,7 +13806,7 @@
         <v>PASS</v>
       </c>
       <c r="L309" t="str">
-        <v>0.117s</v>
+        <v>0.065s</v>
       </c>
       <c r="M309" t="str">
         <v>N/A</v>
@@ -13849,7 +13849,7 @@
         <v>PASS</v>
       </c>
       <c r="L310" t="str">
-        <v>0.093s</v>
+        <v>0.151s</v>
       </c>
       <c r="M310" t="str">
         <v>N/A</v>
@@ -13892,7 +13892,7 @@
         <v>PASS</v>
       </c>
       <c r="L311" t="str">
-        <v>0.085s</v>
+        <v>0.111s</v>
       </c>
       <c r="M311" t="str">
         <v>N/A</v>
@@ -13935,7 +13935,7 @@
         <v>PASS</v>
       </c>
       <c r="L312" t="str">
-        <v>0.170s</v>
+        <v>0.154s</v>
       </c>
       <c r="M312" t="str">
         <v>N/A</v>
@@ -13978,7 +13978,7 @@
         <v>PASS</v>
       </c>
       <c r="L313" t="str">
-        <v>0.144s</v>
+        <v>0.184s</v>
       </c>
       <c r="M313" t="str">
         <v>N/A</v>
@@ -14021,7 +14021,7 @@
         <v>PASS</v>
       </c>
       <c r="L314" t="str">
-        <v>0.157s</v>
+        <v>0.159s</v>
       </c>
       <c r="M314" t="str">
         <v>N/A</v>
@@ -14064,7 +14064,7 @@
         <v>PASS</v>
       </c>
       <c r="L315" t="str">
-        <v>0.067s</v>
+        <v>0.188s</v>
       </c>
       <c r="M315" t="str">
         <v>N/A</v>
@@ -14107,7 +14107,7 @@
         <v>PASS</v>
       </c>
       <c r="L316" t="str">
-        <v>0.056s</v>
+        <v>0.158s</v>
       </c>
       <c r="M316" t="str">
         <v>N/A</v>
@@ -14150,7 +14150,7 @@
         <v>PASS</v>
       </c>
       <c r="L317" t="str">
-        <v>0.096s</v>
+        <v>0.077s</v>
       </c>
       <c r="M317" t="str">
         <v>N/A</v>
@@ -14193,7 +14193,7 @@
         <v>PASS</v>
       </c>
       <c r="L318" t="str">
-        <v>0.170s</v>
+        <v>0.083s</v>
       </c>
       <c r="M318" t="str">
         <v>N/A</v>
@@ -14236,7 +14236,7 @@
         <v>PASS</v>
       </c>
       <c r="L319" t="str">
-        <v>0.146s</v>
+        <v>0.114s</v>
       </c>
       <c r="M319" t="str">
         <v>N/A</v>
@@ -14279,7 +14279,7 @@
         <v>PASS</v>
       </c>
       <c r="L320" t="str">
-        <v>0.125s</v>
+        <v>0.089s</v>
       </c>
       <c r="M320" t="str">
         <v>N/A</v>
@@ -14322,7 +14322,7 @@
         <v>PASS</v>
       </c>
       <c r="L321" t="str">
-        <v>0.179s</v>
+        <v>0.107s</v>
       </c>
       <c r="M321" t="str">
         <v>N/A</v>
@@ -14365,7 +14365,7 @@
         <v>PASS</v>
       </c>
       <c r="L322" t="str">
-        <v>0.185s</v>
+        <v>0.133s</v>
       </c>
       <c r="M322" t="str">
         <v>N/A</v>
@@ -14408,7 +14408,7 @@
         <v>PASS</v>
       </c>
       <c r="L323" t="str">
-        <v>0.176s</v>
+        <v>0.056s</v>
       </c>
       <c r="M323" t="str">
         <v>N/A</v>
@@ -14451,7 +14451,7 @@
         <v>PASS</v>
       </c>
       <c r="L324" t="str">
-        <v>0.079s</v>
+        <v>0.134s</v>
       </c>
       <c r="M324" t="str">
         <v>N/A</v>
@@ -14494,7 +14494,7 @@
         <v>PASS</v>
       </c>
       <c r="L325" t="str">
-        <v>0.051s</v>
+        <v>0.079s</v>
       </c>
       <c r="M325" t="str">
         <v>N/A</v>
@@ -14537,7 +14537,7 @@
         <v>PASS</v>
       </c>
       <c r="L326" t="str">
-        <v>0.166s</v>
+        <v>0.151s</v>
       </c>
       <c r="M326" t="str">
         <v>N/A</v>
@@ -14580,7 +14580,7 @@
         <v>PASS</v>
       </c>
       <c r="L327" t="str">
-        <v>0.059s</v>
+        <v>0.173s</v>
       </c>
       <c r="M327" t="str">
         <v>N/A</v>
@@ -14623,7 +14623,7 @@
         <v>PASS</v>
       </c>
       <c r="L328" t="str">
-        <v>0.052s</v>
+        <v>0.141s</v>
       </c>
       <c r="M328" t="str">
         <v>N/A</v>
@@ -14666,7 +14666,7 @@
         <v>PASS</v>
       </c>
       <c r="L329" t="str">
-        <v>0.089s</v>
+        <v>0.115s</v>
       </c>
       <c r="M329" t="str">
         <v>N/A</v>
@@ -14709,7 +14709,7 @@
         <v>PASS</v>
       </c>
       <c r="L330" t="str">
-        <v>0.148s</v>
+        <v>0.079s</v>
       </c>
       <c r="M330" t="str">
         <v>N/A</v>
@@ -14752,7 +14752,7 @@
         <v>PASS</v>
       </c>
       <c r="L331" t="str">
-        <v>0.066s</v>
+        <v>0.188s</v>
       </c>
       <c r="M331" t="str">
         <v>N/A</v>
@@ -14795,7 +14795,7 @@
         <v>PASS</v>
       </c>
       <c r="L332" t="str">
-        <v>0.187s</v>
+        <v>0.080s</v>
       </c>
       <c r="M332" t="str">
         <v>N/A</v>
@@ -14838,7 +14838,7 @@
         <v>PASS</v>
       </c>
       <c r="L333" t="str">
-        <v>0.066s</v>
+        <v>0.101s</v>
       </c>
       <c r="M333" t="str">
         <v>N/A</v>
@@ -14881,7 +14881,7 @@
         <v>PASS</v>
       </c>
       <c r="L334" t="str">
-        <v>0.170s</v>
+        <v>0.148s</v>
       </c>
       <c r="M334" t="str">
         <v>N/A</v>
@@ -14924,7 +14924,7 @@
         <v>PASS</v>
       </c>
       <c r="L335" t="str">
-        <v>0.145s</v>
+        <v>0.125s</v>
       </c>
       <c r="M335" t="str">
         <v>N/A</v>
@@ -14967,7 +14967,7 @@
         <v>PASS</v>
       </c>
       <c r="L336" t="str">
-        <v>0.173s</v>
+        <v>0.140s</v>
       </c>
       <c r="M336" t="str">
         <v>N/A</v>
@@ -15010,7 +15010,7 @@
         <v>PASS</v>
       </c>
       <c r="L337" t="str">
-        <v>0.110s</v>
+        <v>0.136s</v>
       </c>
       <c r="M337" t="str">
         <v>N/A</v>
@@ -15053,7 +15053,7 @@
         <v>PASS</v>
       </c>
       <c r="L338" t="str">
-        <v>0.092s</v>
+        <v>0.169s</v>
       </c>
       <c r="M338" t="str">
         <v>N/A</v>
@@ -15096,7 +15096,7 @@
         <v>PASS</v>
       </c>
       <c r="L339" t="str">
-        <v>0.132s</v>
+        <v>0.149s</v>
       </c>
       <c r="M339" t="str">
         <v>N/A</v>
@@ -15139,7 +15139,7 @@
         <v>PASS</v>
       </c>
       <c r="L340" t="str">
-        <v>0.119s</v>
+        <v>0.115s</v>
       </c>
       <c r="M340" t="str">
         <v>N/A</v>
@@ -15182,7 +15182,7 @@
         <v>PASS</v>
       </c>
       <c r="L341" t="str">
-        <v>0.098s</v>
+        <v>0.133s</v>
       </c>
       <c r="M341" t="str">
         <v>N/A</v>
@@ -15225,7 +15225,7 @@
         <v>PASS</v>
       </c>
       <c r="L342" t="str">
-        <v>0.052s</v>
+        <v>0.180s</v>
       </c>
       <c r="M342" t="str">
         <v>N/A</v>
@@ -15268,7 +15268,7 @@
         <v>PASS</v>
       </c>
       <c r="L343" t="str">
-        <v>0.117s</v>
+        <v>0.168s</v>
       </c>
       <c r="M343" t="str">
         <v>N/A</v>
@@ -15311,7 +15311,7 @@
         <v>PASS</v>
       </c>
       <c r="L344" t="str">
-        <v>0.153s</v>
+        <v>0.118s</v>
       </c>
       <c r="M344" t="str">
         <v>N/A</v>
@@ -15354,7 +15354,7 @@
         <v>PASS</v>
       </c>
       <c r="L345" t="str">
-        <v>0.122s</v>
+        <v>0.062s</v>
       </c>
       <c r="M345" t="str">
         <v>N/A</v>
@@ -15397,7 +15397,7 @@
         <v>PASS</v>
       </c>
       <c r="L346" t="str">
-        <v>0.122s</v>
+        <v>0.130s</v>
       </c>
       <c r="M346" t="str">
         <v>N/A</v>
@@ -15440,7 +15440,7 @@
         <v>PASS</v>
       </c>
       <c r="L347" t="str">
-        <v>0.097s</v>
+        <v>0.057s</v>
       </c>
       <c r="M347" t="str">
         <v>N/A</v>
@@ -15483,7 +15483,7 @@
         <v>PASS</v>
       </c>
       <c r="L348" t="str">
-        <v>0.175s</v>
+        <v>0.114s</v>
       </c>
       <c r="M348" t="str">
         <v>N/A</v>
@@ -15526,7 +15526,7 @@
         <v>PASS</v>
       </c>
       <c r="L349" t="str">
-        <v>0.183s</v>
+        <v>0.071s</v>
       </c>
       <c r="M349" t="str">
         <v>N/A</v>
@@ -15569,7 +15569,7 @@
         <v>PASS</v>
       </c>
       <c r="L350" t="str">
-        <v>0.164s</v>
+        <v>0.132s</v>
       </c>
       <c r="M350" t="str">
         <v>N/A</v>
@@ -15612,7 +15612,7 @@
         <v>PASS</v>
       </c>
       <c r="L351" t="str">
-        <v>0.050s</v>
+        <v>0.087s</v>
       </c>
       <c r="M351" t="str">
         <v>N/A</v>
@@ -15655,7 +15655,7 @@
         <v>PASS</v>
       </c>
       <c r="L352" t="str">
-        <v>0.099s</v>
+        <v>0.100s</v>
       </c>
       <c r="M352" t="str">
         <v>N/A</v>
@@ -15698,7 +15698,7 @@
         <v>PASS</v>
       </c>
       <c r="L353" t="str">
-        <v>0.108s</v>
+        <v>0.129s</v>
       </c>
       <c r="M353" t="str">
         <v>N/A</v>
@@ -15741,7 +15741,7 @@
         <v>PASS</v>
       </c>
       <c r="L354" t="str">
-        <v>0.130s</v>
+        <v>0.163s</v>
       </c>
       <c r="M354" t="str">
         <v>N/A</v>
@@ -15784,7 +15784,7 @@
         <v>PASS</v>
       </c>
       <c r="L355" t="str">
-        <v>0.181s</v>
+        <v>0.125s</v>
       </c>
       <c r="M355" t="str">
         <v>N/A</v>
@@ -15827,7 +15827,7 @@
         <v>PASS</v>
       </c>
       <c r="L356" t="str">
-        <v>0.104s</v>
+        <v>0.145s</v>
       </c>
       <c r="M356" t="str">
         <v>N/A</v>
